--- a/data/trans_orig/P1435_2011_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1435_2011_2023-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>963109</t>
+          <t>963287</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>972563</t>
+          <t>972633</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1272050</t>
+          <t>1271036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1299923</t>
+          <t>1300324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2238454</t>
+          <t>2241838</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2269463</t>
+          <t>2269771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11534</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37874</t>
+          <t>37473</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65747</t>
+          <t>66761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42977</t>
+          <t>42669</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73986</t>
+          <t>70602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1953381</t>
+          <t>1953347</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1962071</t>
+          <t>1962057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1681049</t>
+          <t>1682130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1712819</t>
+          <t>1713233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3638359</t>
+          <t>3641179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3672014</t>
+          <t>3672489</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44984</t>
+          <t>44570</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76754</t>
+          <t>75673</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>49746</t>
+          <t>49271</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83401</t>
+          <t>80581</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>475358</t>
+          <t>475418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>430664</t>
+          <t>431410</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>448107</t>
+          <t>448481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>910596</t>
+          <t>910564</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>929162</t>
+          <t>928831</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27967</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>29249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3401129</t>
+          <t>3400800</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3413918</t>
+          <t>3413847</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3401135</t>
+          <t>3401916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3448567</t>
+          <t>3448963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6810681</t>
+          <t>6810710</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6858785</t>
+          <t>6859171</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105663</t>
+          <t>105267</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153095</t>
+          <t>152314</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115227</t>
+          <t>114841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>163331</t>
+          <t>163302</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2894,32 +2894,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2929,32 +2929,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>83944</t>
+          <t>87190</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70029</t>
+          <t>74119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103587</t>
+          <t>103086</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2964,32 +2964,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>96969</t>
+          <t>101086</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82661</t>
+          <t>85395</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118950</t>
+          <t>118540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -3007,32 +3007,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>500916</t>
+          <t>563646</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>493067</t>
+          <t>555400</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>506291</t>
+          <t>569500</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3042,32 +3042,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>668593</t>
+          <t>733418</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>648950</t>
+          <t>717522</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>682508</t>
+          <t>746489</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3077,32 +3077,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1169510</t>
+          <t>1297064</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1147529</t>
+          <t>1279610</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1183818</t>
+          <t>1312755</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -3120,17 +3120,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3155,17 +3155,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>752537</t>
+          <t>820608</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>752537</t>
+          <t>820608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>752537</t>
+          <t>820608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3190,17 +3190,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1266479</t>
+          <t>1398150</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1266479</t>
+          <t>1398150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1266479</t>
+          <t>1398150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3350,32 +3350,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>31758</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>21078</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46738</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3385,32 +3385,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>364704</t>
+          <t>183176</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>168264</t>
+          <t>161339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>887926</t>
+          <t>207562</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3420,32 +3420,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>396173</t>
+          <t>214934</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>192521</t>
+          <t>188931</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1104903</t>
+          <t>241967</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -3463,32 +3463,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2257063</t>
+          <t>2196842</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2241794</t>
+          <t>2180587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2267816</t>
+          <t>2207522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3498,32 +3498,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1870676</t>
+          <t>1985691</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1347454</t>
+          <t>1961305</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2067116</t>
+          <t>2007528</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3533,32 +3533,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4127740</t>
+          <t>4182533</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3419010</t>
+          <t>4155500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4331392</t>
+          <t>4208536</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -3576,17 +3576,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2288532</t>
+          <t>2228600</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2288532</t>
+          <t>2228600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2288532</t>
+          <t>2228600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2235380</t>
+          <t>2168867</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2235380</t>
+          <t>2168867</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2235380</t>
+          <t>2168867</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3646,17 +3646,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4523913</t>
+          <t>4397467</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4523913</t>
+          <t>4397467</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4523913</t>
+          <t>4397467</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3806,32 +3806,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3841,32 +3841,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>61315</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45507</t>
+          <t>48627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70560</t>
+          <t>75773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3876,32 +3876,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>69193</t>
+          <t>75235</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57331</t>
+          <t>61891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85205</t>
+          <t>91850</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3919,32 +3919,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>634540</t>
+          <t>697666</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>626454</t>
+          <t>687090</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639883</t>
+          <t>703270</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3954,32 +3954,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>602385</t>
+          <t>671453</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588935</t>
+          <t>656995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>613988</t>
+          <t>684141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3989,32 +3989,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1236926</t>
+          <t>1369120</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1220914</t>
+          <t>1352505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1248788</t>
+          <t>1382464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -4032,17 +4032,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4067,17 +4067,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>659495</t>
+          <t>732768</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>659495</t>
+          <t>732768</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>659495</t>
+          <t>732768</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4102,17 +4102,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1306119</t>
+          <t>1444355</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1306119</t>
+          <t>1444355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1306119</t>
+          <t>1444355</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4262,32 +4262,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>56578</t>
+          <t>59574</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76093</t>
+          <t>77982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4297,32 +4297,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>505758</t>
+          <t>331681</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>309761</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1104685</t>
+          <t>362906</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4332,32 +4332,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>562335</t>
+          <t>391255</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356175</t>
+          <t>356128</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1299004</t>
+          <t>425285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -4375,32 +4375,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3392519</t>
+          <t>3458155</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3373004</t>
+          <t>3439747</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3408926</t>
+          <t>3471883</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4410,32 +4410,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3141655</t>
+          <t>3390562</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2542728</t>
+          <t>3359337</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3337652</t>
+          <t>3418145</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4445,32 +4445,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6534175</t>
+          <t>6848718</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5797506</t>
+          <t>6814688</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6740335</t>
+          <t>6883845</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -4488,17 +4488,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3449097</t>
+          <t>3517729</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3449097</t>
+          <t>3517729</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3449097</t>
+          <t>3517729</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4523,17 +4523,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3647413</t>
+          <t>3722243</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3647413</t>
+          <t>3722243</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3647413</t>
+          <t>3722243</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7096510</t>
+          <t>7239973</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7096510</t>
+          <t>7239973</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7096510</t>
+          <t>7239973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
